--- a/test_data/PD_2025_Jan_Feb.xlsx
+++ b/test_data/PD_2025_Jan_Feb.xlsx
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>210452.04</v>
+        <v>210910.61</v>
       </c>
     </row>
     <row r="3">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>207343.85</v>
+        <v>208004.74</v>
       </c>
     </row>
     <row r="4">
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>211742.02</v>
+        <v>211107.41</v>
       </c>
     </row>
     <row r="5">
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208577.39</v>
+        <v>210041.17</v>
       </c>
     </row>
     <row r="6">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>290068.13</v>
+        <v>292228.9</v>
       </c>
     </row>
     <row r="7">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>288269.24</v>
+        <v>286915.62</v>
       </c>
     </row>
     <row r="8">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>832601.28</v>
+        <v>829216.49</v>
       </c>
     </row>
     <row r="9">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>817856.8199999999</v>
+        <v>821604.33</v>
       </c>
     </row>
     <row r="10">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1211953.52</v>
+        <v>1213675.16</v>
       </c>
     </row>
     <row r="11">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1193310.29</v>
+        <v>1199625.44</v>
       </c>
     </row>
     <row r="12">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>821117.62</v>
+        <v>819105</v>
       </c>
     </row>
     <row r="13">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>808656.13</v>
+        <v>808625.91</v>
       </c>
     </row>
     <row r="14">
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>423698.17</v>
+        <v>424479.02</v>
       </c>
     </row>
     <row r="15">
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>418655.24</v>
+        <v>418202.81</v>
       </c>
     </row>
     <row r="16">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>662699.29</v>
+        <v>665458.39</v>
       </c>
     </row>
     <row r="17">
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658486.89</v>
+        <v>653294</v>
       </c>
     </row>
     <row r="18">
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1086655.24</v>
+        <v>1079467.86</v>
       </c>
     </row>
     <row r="19">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1067212.04</v>
+        <v>1066367.14</v>
       </c>
     </row>
     <row r="20">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>302863.8</v>
+        <v>303419.93</v>
       </c>
     </row>
     <row r="21">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>300283.7</v>
+        <v>300660.32</v>
       </c>
     </row>
     <row r="22">
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>981685.14</v>
+        <v>975907.38</v>
       </c>
     </row>
     <row r="23">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>964274.86</v>
+        <v>969499.0600000001</v>
       </c>
     </row>
     <row r="24">
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>807012.58</v>
+        <v>812305.97</v>
       </c>
     </row>
     <row r="25">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>797695.42</v>
+        <v>798175.9</v>
       </c>
     </row>
     <row r="26">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>256219.68</v>
+        <v>257713.36</v>
       </c>
     </row>
     <row r="27">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>252963.4</v>
+        <v>254339.64</v>
       </c>
     </row>
     <row r="28">
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>950888.9399999999</v>
+        <v>946847.83</v>
       </c>
     </row>
     <row r="29">
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>932824.24</v>
+        <v>939777.96</v>
       </c>
     </row>
     <row r="30">
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>426604.87</v>
+        <v>422869.14</v>
       </c>
     </row>
     <row r="31">
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>417713.2</v>
+        <v>418714.5</v>
       </c>
     </row>
     <row r="32">
@@ -1173,7 +1173,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>788662.35</v>
+        <v>785685.98</v>
       </c>
     </row>
     <row r="33">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>779790.1800000001</v>
+        <v>777643.09</v>
       </c>
     </row>
     <row r="34">
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>626738.91</v>
+        <v>625180.23</v>
       </c>
     </row>
     <row r="35">
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>616475.61</v>
+        <v>621440.78</v>
       </c>
     </row>
     <row r="36">
@@ -1265,7 +1265,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>329983.65</v>
+        <v>330221.38</v>
       </c>
     </row>
     <row r="37">
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>327198.17</v>
+        <v>325585.75</v>
       </c>
     </row>
     <row r="38">
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1074418.85</v>
+        <v>1075798.66</v>
       </c>
     </row>
     <row r="39">
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1061507.05</v>
+        <v>1062770.77</v>
       </c>
     </row>
     <row r="40">
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>186710.65</v>
+        <v>186522.1</v>
       </c>
     </row>
     <row r="41">
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>184487.43</v>
+        <v>184852.44</v>
       </c>
     </row>
     <row r="42">
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>788474.46</v>
+        <v>788434.63</v>
       </c>
     </row>
     <row r="43">
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>782220.96</v>
+        <v>778658.3</v>
       </c>
     </row>
     <row r="44">
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>892335.45</v>
+        <v>890367.13</v>
       </c>
     </row>
     <row r="45">
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>878644.97</v>
+        <v>881955.29</v>
       </c>
     </row>
     <row r="46">
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1163376.66</v>
+        <v>1159226.7</v>
       </c>
     </row>
     <row r="47">
@@ -1518,7 +1518,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1152225.91</v>
+        <v>1142760.85</v>
       </c>
     </row>
     <row r="48">
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1222315.51</v>
+        <v>1228232.59</v>
       </c>
     </row>
     <row r="49">
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1208341.78</v>
+        <v>1207104.41</v>
       </c>
     </row>
     <row r="50">
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>499417.63</v>
+        <v>498880.79</v>
       </c>
     </row>
     <row r="51">
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>495919.63</v>
+        <v>495006.51</v>
       </c>
     </row>
     <row r="52">
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>346623.23</v>
+        <v>347137.08</v>
       </c>
     </row>
     <row r="53">
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>341955.36</v>
+        <v>340952.06</v>
       </c>
     </row>
     <row r="54">
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>475058.12</v>
+        <v>471362.06</v>
       </c>
     </row>
     <row r="55">
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>466117.51</v>
+        <v>469651.02</v>
       </c>
     </row>
     <row r="56">
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1130825.24</v>
+        <v>1132725.16</v>
       </c>
     </row>
     <row r="57">
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1111599.64</v>
+        <v>1116852.76</v>
       </c>
     </row>
     <row r="58">
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1156442.49</v>
+        <v>1153913.32</v>
       </c>
     </row>
     <row r="59">
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1146589.76</v>
+        <v>1149436.27</v>
       </c>
     </row>
     <row r="60">
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1092638.34</v>
+        <v>1082605.47</v>
       </c>
     </row>
     <row r="61">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1079870.02</v>
+        <v>1075606.43</v>
       </c>
     </row>
     <row r="62">
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2093539.96</v>
+        <v>2108260.25</v>
       </c>
     </row>
     <row r="63">
@@ -1886,7 +1886,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2074655.35</v>
+        <v>2084450.69</v>
       </c>
     </row>
     <row r="64">
@@ -1909,7 +1909,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1008476.27</v>
+        <v>1005503.21</v>
       </c>
     </row>
     <row r="65">
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1001223.79</v>
+        <v>995875.4</v>
       </c>
     </row>
     <row r="66">
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1658951.72</v>
+        <v>1650803.72</v>
       </c>
     </row>
     <row r="67">
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1643165.88</v>
+        <v>1639269.67</v>
       </c>
     </row>
     <row r="68">
@@ -2001,7 +2001,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1924635.42</v>
+        <v>1943069.1</v>
       </c>
     </row>
     <row r="69">
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1906957.8</v>
+        <v>1913313.8</v>
       </c>
     </row>
     <row r="70">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1124125.89</v>
+        <v>1116278.16</v>
       </c>
     </row>
     <row r="71">
@@ -2070,7 +2070,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1108896.89</v>
+        <v>1109337.14</v>
       </c>
     </row>
     <row r="72">
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2018925.16</v>
+        <v>2024121.61</v>
       </c>
     </row>
     <row r="73">
@@ -2116,7 +2116,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1997106.75</v>
+        <v>2001694.1</v>
       </c>
     </row>
     <row r="74">
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1858157.55</v>
+        <v>1862621.55</v>
       </c>
     </row>
     <row r="75">
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1849483.34</v>
+        <v>1834293.14</v>
       </c>
     </row>
     <row r="76">
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2144525.52</v>
+        <v>2133923.54</v>
       </c>
     </row>
     <row r="77">
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2117655.96</v>
+        <v>2114911.62</v>
       </c>
     </row>
     <row r="78">
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1271365.42</v>
+        <v>1270632.77</v>
       </c>
     </row>
     <row r="79">
@@ -2254,7 +2254,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1258614.64</v>
+        <v>1253600.9</v>
       </c>
     </row>
     <row r="80">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1610597.51</v>
+        <v>1602852.52</v>
       </c>
     </row>
     <row r="81">
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1584066.02</v>
+        <v>1596292.12</v>
       </c>
     </row>
     <row r="82">
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2329725.86</v>
+        <v>2335348.71</v>
       </c>
     </row>
     <row r="83">
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2295211.42</v>
+        <v>2311014.56</v>
       </c>
     </row>
     <row r="84">
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1749078.08</v>
+        <v>1763684.22</v>
       </c>
     </row>
     <row r="85">
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1740332.98</v>
+        <v>1732798.98</v>
       </c>
     </row>
     <row r="86">
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1289317.74</v>
+        <v>1291949.31</v>
       </c>
     </row>
     <row r="87">
@@ -2438,7 +2438,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1268630.74</v>
+        <v>1268529.39</v>
       </c>
     </row>
     <row r="88">
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>420991.38</v>
+        <v>423648.13</v>
       </c>
     </row>
     <row r="89">
@@ -2484,7 +2484,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>415341.45</v>
+        <v>417115.89</v>
       </c>
     </row>
     <row r="90">
@@ -2507,7 +2507,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1459675.15</v>
+        <v>1453631.36</v>
       </c>
     </row>
     <row r="91">
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1441524.53</v>
+        <v>1434234.47</v>
       </c>
     </row>
     <row r="92">
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>592910.47</v>
+        <v>588700.8</v>
       </c>
     </row>
     <row r="93">
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>585859.41</v>
+        <v>581453.95</v>
       </c>
     </row>
     <row r="94">
@@ -2599,7 +2599,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>951783.64</v>
+        <v>956257.02</v>
       </c>
     </row>
     <row r="95">
@@ -2622,7 +2622,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>937404.25</v>
+        <v>939564.1</v>
       </c>
     </row>
     <row r="96">
@@ -2645,7 +2645,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1742575.61</v>
+        <v>1751798.73</v>
       </c>
     </row>
     <row r="97">
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1719855.48</v>
+        <v>1727162.11</v>
       </c>
     </row>
     <row r="98">
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2484400.68</v>
+        <v>2481504.23</v>
       </c>
     </row>
     <row r="99">
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2460383.1</v>
+        <v>2448398.11</v>
       </c>
     </row>
     <row r="100">
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2241167.51</v>
+        <v>2241629.06</v>
       </c>
     </row>
     <row r="101">
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2208041.58</v>
+        <v>2212627.97</v>
       </c>
     </row>
     <row r="102">
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4465724.85</v>
+        <v>4479105.01</v>
       </c>
     </row>
     <row r="103">
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4410360.11</v>
+        <v>4402311.38</v>
       </c>
     </row>
     <row r="104">
@@ -2829,7 +2829,7 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4920159.63</v>
+        <v>4920965.88</v>
       </c>
     </row>
     <row r="105">
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4853581.24</v>
+        <v>4833265.19</v>
       </c>
     </row>
     <row r="106">
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>3795224.99</v>
+        <v>3774275.01</v>
       </c>
     </row>
     <row r="107">
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>3740061.89</v>
+        <v>3736939.49</v>
       </c>
     </row>
     <row r="108">
@@ -2921,7 +2921,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4110780.5</v>
+        <v>4091768.31</v>
       </c>
     </row>
     <row r="109">
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4047491.17</v>
+        <v>4046863.63</v>
       </c>
     </row>
     <row r="110">
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>3388793.59</v>
+        <v>3393922.32</v>
       </c>
     </row>
     <row r="111">
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>3372997.41</v>
+        <v>3365613.56</v>
       </c>
     </row>
     <row r="112">
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2091790.26</v>
+        <v>2082084.25</v>
       </c>
     </row>
     <row r="113">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2067538.35</v>
+        <v>2063984.92</v>
       </c>
     </row>
     <row r="114">
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2906314.25</v>
+        <v>2900152.89</v>
       </c>
     </row>
     <row r="115">
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2878759.54</v>
+        <v>2858378.47</v>
       </c>
     </row>
     <row r="116">
@@ -3105,7 +3105,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2013003.57</v>
+        <v>2016802.17</v>
       </c>
     </row>
     <row r="117">
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1984483.32</v>
+        <v>1992872.62</v>
       </c>
     </row>
     <row r="118">
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4175537.23</v>
+        <v>4190489.67</v>
       </c>
     </row>
     <row r="119">
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4157510.47</v>
+        <v>4128023.86</v>
       </c>
     </row>
     <row r="120">
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5094487.93</v>
+        <v>5130579.74</v>
       </c>
     </row>
     <row r="121">
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5028855.41</v>
+        <v>5050807.09</v>
       </c>
     </row>
   </sheetData>
